--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484869_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484869_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0774</v>
+        <v>3.9967</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5355</v>
+        <v>1.2432</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5419</v>
+        <v>2.7535</v>
       </c>
       <c r="G2" t="n">
         <v>5.0591</v>
@@ -610,13 +610,13 @@
         <v>1.3209</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.057</v>
+        <v>-0.1377</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1582</v>
+        <v>-0.4505</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1012</v>
+        <v>0.3128</v>
       </c>
       <c r="V2" t="n">
         <v>-1.3021</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6404</v>
+        <v>0.6241</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5457</v>
+        <v>-0.2854</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0947</v>
+        <v>0.9095</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9912</v>
@@ -688,13 +688,13 @@
         <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2543</v>
+        <v>1.238</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6628</v>
+        <v>0.8317</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5914</v>
+        <v>0.4063</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. MALONE NAVARRO</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1284</v>
+        <v>0.0631</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1894</v>
+        <v>-0.288</v>
       </c>
       <c r="F4" t="n">
-        <v>0.061</v>
+        <v>0.3511</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0388</v>
+        <v>-0.8159</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3921</v>
+        <v>-0.5736</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4309</v>
+        <v>-0.2423</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1045</v>
+        <v>-0.0015</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0634</v>
+        <v>0.5658</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0411</v>
+        <v>-0.5673</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.8144</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4555</v>
+        <v>-1.1394</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3897</v>
+        <v>0.325</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0541</v>
+        <v>-0.1401</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2939</v>
+        <v>-0.2865</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2399</v>
+        <v>0.1464</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3018</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6514</v>
+        <v>-0.1235</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.4171</v>
+        <v>-1.9685</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7656</v>
+        <v>1.845</v>
       </c>
       <c r="G5" t="n">
         <v>-1.1943</v>
@@ -844,13 +844,13 @@
         <v>1.5096</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6649</v>
+        <v>-0.137</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.585</v>
+        <v>-0.1365</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0799</v>
+        <v>-0.0005</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3018</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. GONZALEZ DIAZ</t>
+          <t>B. MALONE NAVARRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9853</v>
+        <v>-0.1632</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.1173</v>
+        <v>-0.092</v>
       </c>
       <c r="F6" t="n">
-        <v>3.132</v>
+        <v>-0.0712</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5874</v>
+        <v>0.0388</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4948</v>
+        <v>-0.3921</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9074</v>
+        <v>0.4309</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.305</v>
+        <v>0.1045</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6965</v>
+        <v>0.0634</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0.0411</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7176</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7982</v>
+        <v>-0.4555</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5158</v>
+        <v>0.3897</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3209</v>
+        <v>0.1887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1716</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9254</v>
+        <v>-0.1965</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7537</v>
+        <v>0.1076</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3398</v>
+        <v>-0.3018</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3398</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>C. GONZALEZ DIAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2753</v>
+        <v>-0.6691</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2825</v>
+        <v>-3.6688</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0072</v>
+        <v>2.9997</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8159</v>
+        <v>-0.5874</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5736</v>
+        <v>-1.4948</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2423</v>
+        <v>0.9074</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0015</v>
+        <v>-1.305</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5658</v>
+        <v>-0.6965</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5673</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8144</v>
+        <v>0.7176</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1394</v>
+        <v>-0.7982</v>
       </c>
       <c r="O7" t="n">
-        <v>0.325</v>
+        <v>1.5158</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3209</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R7" t="n">
         <v>1.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4785</v>
+        <v>0.1446</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.281</v>
+        <v>-0.4768</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1975</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3018</v>
+        <v>0.3398</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3018</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5328</v>
+        <v>-2.9393</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.4552</v>
+        <v>-3.6501</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9224</v>
+        <v>0.7108</v>
       </c>
       <c r="G8" t="n">
         <v>1.0417</v>
@@ -1078,13 +1078,13 @@
         <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>0.388</v>
+        <v>-0.0185</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2199</v>
+        <v>-0.4148</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6079</v>
+        <v>0.3963</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8868</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3284</v>
+        <v>-4.1917</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.0289</v>
+        <v>-3.6188</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7005</v>
+        <v>-0.5729</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2334</v>
+        <v>-4.5087</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6762</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9096</v>
+        <v>-3.8106</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2686</v>
+        <v>-3.733</v>
       </c>
       <c r="K9" t="n">
-        <v>1.897</v>
+        <v>0.1643</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.1655</v>
+        <v>-3.8974</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0352</v>
+        <v>-0.7756</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2208</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.256</v>
+        <v>0.0868</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6983</v>
+        <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2069</v>
+        <v>0.317</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2881</v>
+        <v>-0.1874</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4951</v>
+        <v>0.5044</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2262</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.528</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0971</v>
+        <v>-4.2902</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4184</v>
+        <v>-4.9113</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6787</v>
+        <v>0.6211</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.5087</v>
+        <v>-1.2334</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6981000000000001</v>
+        <v>0.6762</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.8106</v>
+        <v>-1.9096</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.733</v>
+        <v>-1.2686</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1643</v>
+        <v>1.897</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.8974</v>
+        <v>-3.1655</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7756</v>
+        <v>0.0352</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-1.2208</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0868</v>
+        <v>1.256</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9435</v>
+        <v>-3.774</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5885</v>
+        <v>0.2451</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9871</v>
+        <v>-0.1706</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3986</v>
+        <v>0.4157</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2262</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2452</v>
+        <v>-1.528</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.280899999999999</v>
+        <v>-7.693099999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-17.8276</v>
+        <v>-17.2397</v>
       </c>
       <c r="F11" t="n">
-        <v>9.546600000000002</v>
+        <v>9.5466</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1913</v>
@@ -1297,13 +1297,13 @@
         <v>1.4456</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.025799999999999</v>
+        <v>-6.0258</v>
       </c>
       <c r="O11" t="n">
         <v>7.4711</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9434999999999998</v>
+        <v>-0.9435000000000002</v>
       </c>
       <c r="Q11" t="n">
         <v>-11.322</v>
@@ -1312,13 +1312,13 @@
         <v>10.3785</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8346</v>
+        <v>1.4225</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.0758</v>
+        <v>-1.4879</v>
       </c>
       <c r="U11" t="n">
-        <v>2.9104</v>
+        <v>2.9105</v>
       </c>
       <c r="V11" t="n">
         <v>-4.980700000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.9001</v>
+        <v>5.1565</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2336</v>
+        <v>1.9157</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6665</v>
+        <v>3.2409</v>
       </c>
       <c r="G12" t="n">
         <v>2.9028</v>
@@ -1390,13 +1390,13 @@
         <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1533</v>
+        <v>0.1031</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.281</v>
+        <v>-0.599</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1276</v>
+        <v>0.702</v>
       </c>
       <c r="V12" t="n">
         <v>2.1506</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9558</v>
+        <v>4.0425</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.761</v>
+        <v>-0.5661</v>
       </c>
       <c r="F13" t="n">
-        <v>4.7168</v>
+        <v>4.6086</v>
       </c>
       <c r="G13" t="n">
         <v>2.1943</v>
@@ -1468,13 +1468,13 @@
         <v>1.887</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2574</v>
+        <v>-0.1707</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.6253</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5627</v>
+        <v>0.4545</v>
       </c>
       <c r="V13" t="n">
         <v>1.2642</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. BLASCO NAVARRO</t>
+          <t>P. LOPEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8704</v>
+        <v>3.0562</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6445</v>
+        <v>-0.2781</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2259</v>
+        <v>3.3343</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5315</v>
+        <v>2.3795</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7568</v>
+        <v>1.5503</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2252</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5211</v>
+        <v>0.5466</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5125999999999999</v>
+        <v>1.7961</v>
       </c>
       <c r="L14" t="n">
-        <v>0.008500000000000001</v>
+        <v>-1.2495</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0526</v>
+        <v>1.8329</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2693</v>
+        <v>-0.2457</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2167</v>
+        <v>2.0786</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7548</v>
+        <v>1.887</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9435</v>
+        <v>1.887</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6848</v>
+        <v>-1.2102</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3121</v>
+        <v>-0.8247</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3727</v>
+        <v>-0.3856</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9624</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.9624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. LOPEZ DOMINGUEZ</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0785</v>
+        <v>2.513</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5704</v>
+        <v>0.0148</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6489</v>
+        <v>2.4982</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3795</v>
+        <v>2.0772</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5503</v>
+        <v>2.9911</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8290999999999999</v>
+        <v>-0.9139</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5466</v>
+        <v>1.3865</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7961</v>
+        <v>3.3182</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2495</v>
+        <v>-1.9316</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8329</v>
+        <v>0.6906</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2457</v>
+        <v>-0.3271</v>
       </c>
       <c r="O15" t="n">
-        <v>2.0786</v>
+        <v>1.0177</v>
       </c>
       <c r="P15" t="n">
-        <v>1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R15" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.188</v>
+        <v>0.1531</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.117</v>
+        <v>-0.2014</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.071</v>
+        <v>0.3545</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.9054</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>L. BLASCO NAVARRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9478</v>
+        <v>2.0286</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.18</v>
+        <v>0.2547</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1278</v>
+        <v>1.7739</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0772</v>
+        <v>-0.5315</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9911</v>
+        <v>-0.7568</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9139</v>
+        <v>0.2252</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3865</v>
+        <v>0.5211</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3182</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.9316</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6906</v>
+        <v>-1.0526</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3271</v>
+        <v>-1.2693</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0177</v>
+        <v>0.2167</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9435</v>
+        <v>0.7548</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0757</v>
+        <v>-0.1887</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1322</v>
+        <v>0.9435</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4121</v>
+        <v>0.843</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3963</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0158</v>
+        <v>0.9206</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2262</v>
+        <v>0.9624</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9054</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3208</v>
+        <v>0.9624</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6334</v>
+        <v>1.5769</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0534</v>
+        <v>-0.2389</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5801</v>
+        <v>1.8158</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7557</v>
@@ -1780,13 +1780,13 @@
         <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3656</v>
+        <v>-0.4222</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1023</v>
+        <v>-0.3946</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2633</v>
+        <v>-0.0276</v>
       </c>
       <c r="V17" t="n">
         <v>1.2452</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3675</v>
+        <v>-1.9786</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0323</v>
+        <v>-1.6169</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3352</v>
+        <v>-0.3616</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6345</v>
@@ -1858,13 +1858,13 @@
         <v>0.3774</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0217</v>
+        <v>0.4106</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.1266</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3104</v>
+        <v>0.284</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9434</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9708</v>
+        <v>-3.0599</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.1079</v>
+        <v>-5.3027</v>
       </c>
       <c r="F19" t="n">
-        <v>2.137</v>
+        <v>2.2429</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4483</v>
@@ -1936,13 +1936,13 @@
         <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3903</v>
+        <v>-0.4794</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2323</v>
+        <v>-0.4271</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1581</v>
+        <v>-0.0522</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6226</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.7667</v>
+        <v>-4.4047</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.1472</v>
+        <v>-4.0498</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.3549</v>
       </c>
       <c r="G20" t="n">
         <v>-2.9923</v>
@@ -2014,13 +2014,13 @@
         <v>0.3774</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2257</v>
+        <v>0.5877</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0152</v>
+        <v>0.1127</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2105</v>
+        <v>0.475</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3018</v>
@@ -2047,16 +2047,16 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>8.280999999999999</v>
+        <v>8.930500000000002</v>
       </c>
       <c r="E21" t="n">
         <v>-9.8673</v>
       </c>
       <c r="F21" t="n">
-        <v>18.1483</v>
+        <v>18.7981</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1915</v>
+        <v>3.191499999999999</v>
       </c>
       <c r="H21" t="n">
         <v>1.7845</v>
@@ -2074,7 +2074,7 @@
         <v>-7.4712</v>
       </c>
       <c r="M21" t="n">
-        <v>4.636900000000001</v>
+        <v>4.6369</v>
       </c>
       <c r="N21" t="n">
         <v>-4.2413</v>
@@ -2083,7 +2083,7 @@
         <v>8.8781</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9435</v>
+        <v>0.9435000000000004</v>
       </c>
       <c r="Q21" t="n">
         <v>-10.3785</v>
@@ -2092,22 +2092,22 @@
         <v>11.322</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8345</v>
+        <v>-0.1849999999999998</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.910499999999999</v>
+        <v>-2.9105</v>
       </c>
       <c r="U21" t="n">
-        <v>2.0757</v>
+        <v>2.7252</v>
       </c>
       <c r="V21" t="n">
-        <v>4.980799999999999</v>
+        <v>4.9808</v>
       </c>
       <c r="W21" t="n">
         <v>4.8668</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1138999999999999</v>
+        <v>0.1139000000000001</v>
       </c>
     </row>
   </sheetData>
